--- a/mock-data/pricing-master-data.xlsx
+++ b/mock-data/pricing-master-data.xlsx
@@ -539,7 +539,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-CHM-9200</t>
+          <t>SKU-FIN-9200</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>CONTRACT-ACME-2026-007</t>
+          <t>CONTRACT-GLP-2026-007</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -911,7 +911,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>CONTRACT-ACME-2026-007</t>
+          <t>CONTRACT-GLP-2026-007</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -956,7 +956,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>CONTRACT-ACME-2026-007</t>
+          <t>CONTRACT-GLP-2026-007</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>CONTRACT-ACME-2025-099</t>
+          <t>CONTRACT-GLP-2025-099</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -1046,7 +1046,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>CONTRACT-GLOBEX-2026-001</t>
+          <t>CONTRACT-PCBK-2026-010</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -1161,7 +1161,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>VT-PIPE-1</t>
+          <t>VT-CTG-1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -1185,14 +1185,14 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>VT-PIPE-2</t>
+          <t>VT-CTG-2</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -1216,14 +1216,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>VT-PIPE-3</t>
+          <t>VT-CTG-3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -1247,14 +1247,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>EA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>VT-FLG-1</t>
+          <t>VT-DRN-1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>FLANGE</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -1285,7 +1285,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>VT-FLG-2</t>
+          <t>VT-DRN-2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FLANGE</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1394,7 +1394,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1436,7 +1436,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>RB-ACME-01</t>
+          <t>RB-GLP-01</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Annual volume &gt; 10000 FT</t>
+          <t>Annual volume &gt; 10000 EA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>RB-ACME-02</t>
+          <t>RB-GLP-02</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1556,7 +1556,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PROMO-Q3-GASKET</t>
+          <t>PROMO-Q3-SEAL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>SEAL</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Q3 gasket promotion</t>
+          <t>Q3 seal kit promotion</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PIPE</t>
+          <t>CARTRIDGE</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1955,7 +1955,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FLANGE</t>
+          <t>DRAIN</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -1991,7 +1991,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>SHOWERSYS</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -2009,7 +2009,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GASKET</t>
+          <t>SEAL</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -2027,7 +2027,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -2059,7 +2059,7 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -2097,7 +2097,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Carbon Steel</t>
+          <t>Brass</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2110,14 +2110,14 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Steel index up 1.5%</t>
+          <t>Brass index up 1.5%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SS316</t>
+          <t>Ceramic</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -2126,18 +2126,18 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Stainless surcharge</t>
+          <t>Ceramic surcharge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Cast Iron</t>
+          <t>Enameled Cast Iron</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">

--- a/mock-data/pricing-master-data.xlsx
+++ b/mock-data/pricing-master-data.xlsx
@@ -795,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -807,6 +807,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -862,6 +863,11 @@
           <t>status</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>margin_floor_pct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -907,6 +913,9 @@
           <t>ACTIVE</t>
         </is>
       </c>
+      <c r="J3" s="3" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -952,6 +961,9 @@
           <t>ACTIVE</t>
         </is>
       </c>
+      <c r="J4" s="4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -997,6 +1009,9 @@
           <t>ACTIVE</t>
         </is>
       </c>
+      <c r="J5" s="3" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1042,6 +1057,9 @@
           <t>EXPIRED</t>
         </is>
       </c>
+      <c r="J6" s="4" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1087,10 +1105,13 @@
           <t>ACTIVE</t>
         </is>
       </c>
+      <c r="J7" s="3" t="n">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1602,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1612,6 +1633,9 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1657,6 +1681,21 @@
           <t>reason</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>valid_from</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>valid_to</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1692,6 +1731,21 @@
           <t>West coast handling surcharge</t>
         </is>
       </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1727,10 +1781,25 @@
           <t>Fuel adjustment</t>
         </is>
       </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mock-data/pricing-master-data.xlsx
+++ b/mock-data/pricing-master-data.xlsx
@@ -14,8 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surcharges" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freight_Terms" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin_Policy" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Material_Index" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax_Rates" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin_Policy" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Material_Index" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -789,6 +790,118 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RAW MATERIAL INDEX  (material cost adjustments)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>index_date</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>index_pct_adjustment</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Brass</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Brass index up 1.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ceramic</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Ceramic surcharge</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Enameled Cast Iron</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>No change</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -887,11 +1000,11 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SKU-CTG-4520</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>10.8</v>
+        <v>1150</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -914,7 +1027,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -1811,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1819,7 +1932,9 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1857,6 +1972,16 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>min_freight</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>per_kg_rate</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -1885,9 +2010,15 @@
       <c r="E3" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Prepaid &amp; add</t>
+      <c r="F3" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Prepaid &amp; add; billed per KG above minimum</t>
         </is>
       </c>
     </row>
@@ -1915,9 +2046,15 @@
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Collect</t>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Collect — buyer arranges carrier</t>
         </is>
       </c>
     </row>
@@ -1945,21 +2082,285 @@
       <c r="E5" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Default freight</t>
+      <c r="F5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Default freight; billed per KG above minimum</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SALES TAX RATES  (state-level sales tax applied by the AI at pricing)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>region_code</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>region_name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>tax_type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>tax_pct</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>SALES_TAX</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>6.25% state + ~2.5% local (Chicago typical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>SALES_TAX</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>7.25% state + ~2.25% local (LA typical)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SALES_TAX</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>8.875</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>4% state + 4.875% local (NYC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>SALES_TAX</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>6% state (no local sales tax)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>SALES_TAX</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>6.25% state + ~2% local</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>SALES_TAX</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>6% state + ~1% local</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Standard VAT rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>SALES_TAX</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Fallback when ship-to state is unknown</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2117,116 +2518,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>RAW MATERIAL INDEX  (material cost adjustments)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>material</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>index_date</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>index_pct_adjustment</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Brass</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Brass index up 1.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Ceramic</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Ceramic surcharge</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Enameled Cast Iron</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>No change</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/mock-data/pricing-master-data.xlsx
+++ b/mock-data/pricing-master-data.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-4600</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>45</v>
+        <v>13.75</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-CTG-4800</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>88</v>
+        <v>15.9</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1450</v>
+        <v>45</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-FIN-9100</t>
+          <t>SKU-VLV-2201</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -689,11 +689,11 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>9.75</v>
+        <v>88</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-FIN-9200</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -724,11 +724,11 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>14</v>
+        <v>1450</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>GAL</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -750,33 +750,173 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>SKU-FIN-9100</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>GAL</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>PL-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SKU-FIN-9200</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>GAL</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>PL-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>SKU-SEL-1150</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C11" s="3" t="n">
         <v>6.25</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>PL-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-CTG-1017</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>PL-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SKU-DRN-7213</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>KIT</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>PL-2026</t>
         </is>

--- a/mock-data/pricing-master-data.xlsx
+++ b/mock-data/pricing-master-data.xlsx
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1150</v>
+        <v>1350</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
